--- a/Rangesayacv5.xlsx
+++ b/Rangesayacv5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B65AC75-B1E1-4A3F-BE6B-2B50517D765F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC5E1F0-3F18-4DE0-BEF7-674AE074E2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{586848BF-8DA1-41BE-9680-FDF5F1E34B0D}"/>
   </bookViews>
@@ -4373,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="K97" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
